--- a/入力シート.xlsx
+++ b/入力シート.xlsx
@@ -287,6 +287,21 @@
     <comment ref="Y3" authorId="0" shapeId="0">
       <text>
         <t>セル内改行で箇条書き</t>
+      </text>
+    </comment>
+    <comment ref="Z3" authorId="0" shapeId="0">
+      <text>
+        <t>この欄だけでも可。見出しは付けずにそのまま印字します</t>
+      </text>
+    </comment>
+    <comment ref="AA3" authorId="0" shapeId="0">
+      <text>
+        <t>任意。志望の動機に続けて印字します</t>
+      </text>
+    </comment>
+    <comment ref="AB3" authorId="0" shapeId="0">
+      <text>
+        <t>任意。最後に続けて印字します</t>
       </text>
     </comment>
   </commentList>
@@ -610,9 +625,9 @@
     <col width="22" customWidth="1" min="23" max="23"/>
     <col width="12" customWidth="1" min="24" max="24"/>
     <col width="34" customWidth="1" min="25" max="25"/>
-    <col width="18" customWidth="1" min="26" max="26"/>
-    <col width="34" customWidth="1" min="27" max="27"/>
-    <col width="40" customWidth="1" min="28" max="28"/>
+    <col width="40" customWidth="1" min="26" max="26"/>
+    <col width="18" customWidth="1" min="27" max="27"/>
+    <col width="34" customWidth="1" min="28" max="28"/>
     <col width="11" customWidth="1" min="29" max="29"/>
     <col width="26" customWidth="1" min="30" max="30"/>
     <col width="11" customWidth="1" min="31" max="31"/>
@@ -827,17 +842,17 @@
       </c>
       <c r="Z3" s="5" t="inlineStr">
         <is>
+          <t>志望の動機</t>
+        </is>
+      </c>
+      <c r="AA3" s="5" t="inlineStr">
+        <is>
           <t>希望の職種</t>
         </is>
       </c>
-      <c r="AA3" s="5" t="inlineStr">
+      <c r="AB3" s="5" t="inlineStr">
         <is>
           <t>アピールポイント</t>
-        </is>
-      </c>
-      <c r="AB3" s="5" t="inlineStr">
-        <is>
-          <t>志望の動機</t>
         </is>
       </c>
       <c r="AC3" s="5" t="inlineStr">
@@ -994,17 +1009,17 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
+          <t>motivation</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
           <t>desired_job</t>
         </is>
       </c>
-      <c r="AA4" t="inlineStr">
+      <c r="AB4" t="inlineStr">
         <is>
           <t>appeal</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>motivation</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">

--- a/入力シート.xlsx
+++ b/入力シート.xlsx
@@ -2638,7 +2638,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C47"/>
+  <dimension ref="A1:C73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -2680,12 +2680,12 @@
     <row r="4">
       <c r="A4" s="10" t="inlineStr">
         <is>
-          <t>英検5級</t>
+          <t>実用英語検定5級</t>
         </is>
       </c>
       <c r="B4" s="10" t="inlineStr">
         <is>
-          <t>実用英語技能検定5級</t>
+          <t>実用英語検定5級</t>
         </is>
       </c>
       <c r="C4" s="12" t="n"/>
@@ -2693,12 +2693,12 @@
     <row r="5">
       <c r="A5" s="10" t="inlineStr">
         <is>
-          <t>英検4級</t>
+          <t>実用英語検定4級</t>
         </is>
       </c>
       <c r="B5" s="10" t="inlineStr">
         <is>
-          <t>実用英語技能検定4級</t>
+          <t>実用英語検定4級</t>
         </is>
       </c>
       <c r="C5" s="12" t="n"/>
@@ -2706,12 +2706,12 @@
     <row r="6">
       <c r="A6" s="10" t="inlineStr">
         <is>
-          <t>英検3級</t>
+          <t>実用英語検定3級</t>
         </is>
       </c>
       <c r="B6" s="10" t="inlineStr">
         <is>
-          <t>実用英語技能検定3級</t>
+          <t>実用英語検定3級</t>
         </is>
       </c>
       <c r="C6" s="12" t="n"/>
@@ -2719,12 +2719,12 @@
     <row r="7">
       <c r="A7" s="10" t="inlineStr">
         <is>
-          <t>英検準2級</t>
+          <t>実用英語検定準２級</t>
         </is>
       </c>
       <c r="B7" s="10" t="inlineStr">
         <is>
-          <t>実用英語技能検定準2級</t>
+          <t>実用英語検定準２級</t>
         </is>
       </c>
       <c r="C7" s="12" t="n"/>
@@ -2732,12 +2732,12 @@
     <row r="8">
       <c r="A8" s="10" t="inlineStr">
         <is>
-          <t>英検2級</t>
+          <t>実用英語検定2級</t>
         </is>
       </c>
       <c r="B8" s="10" t="inlineStr">
         <is>
-          <t>実用英語技能検定2級</t>
+          <t>実用英語検定2級</t>
         </is>
       </c>
       <c r="C8" s="12" t="n"/>
@@ -2745,12 +2745,12 @@
     <row r="9">
       <c r="A9" s="10" t="inlineStr">
         <is>
-          <t>英検準1級</t>
+          <t>実用英語検定1級</t>
         </is>
       </c>
       <c r="B9" s="10" t="inlineStr">
         <is>
-          <t>実用英語技能検定準1級</t>
+          <t>実用英語検定1級</t>
         </is>
       </c>
       <c r="C9" s="12" t="n"/>
@@ -2758,12 +2758,12 @@
     <row r="10">
       <c r="A10" s="10" t="inlineStr">
         <is>
-          <t>実用英語検定3級</t>
+          <t>日本漢字能力検定4級</t>
         </is>
       </c>
       <c r="B10" s="10" t="inlineStr">
         <is>
-          <t>実用英語技能検定3級</t>
+          <t>日本漢字能力検定4級</t>
         </is>
       </c>
       <c r="C10" s="12" t="n"/>
@@ -2771,12 +2771,12 @@
     <row r="11">
       <c r="A11" s="10" t="inlineStr">
         <is>
-          <t>実用英語検定準2級</t>
+          <t>日本漢字能力検定3級</t>
         </is>
       </c>
       <c r="B11" s="10" t="inlineStr">
         <is>
-          <t>実用英語技能検定準2級</t>
+          <t>日本漢字能力検定3級</t>
         </is>
       </c>
       <c r="C11" s="12" t="n"/>
@@ -2784,12 +2784,12 @@
     <row r="12">
       <c r="A12" s="10" t="inlineStr">
         <is>
-          <t>実用英語検定2級</t>
+          <t>日本漢字能力検定準2級</t>
         </is>
       </c>
       <c r="B12" s="10" t="inlineStr">
         <is>
-          <t>実用英語技能検定2級</t>
+          <t>日本漢字能力検定準2級</t>
         </is>
       </c>
       <c r="C12" s="12" t="n"/>
@@ -2797,12 +2797,12 @@
     <row r="13">
       <c r="A13" s="10" t="inlineStr">
         <is>
-          <t>漢検4級</t>
+          <t>日本漢字能力検定2級</t>
         </is>
       </c>
       <c r="B13" s="10" t="inlineStr">
         <is>
-          <t>日本漢字能力検定4級</t>
+          <t>日本漢字能力検定2級</t>
         </is>
       </c>
       <c r="C13" s="12" t="n"/>
@@ -2810,12 +2810,12 @@
     <row r="14">
       <c r="A14" s="10" t="inlineStr">
         <is>
-          <t>漢検3級</t>
+          <t>計算技術検定1級</t>
         </is>
       </c>
       <c r="B14" s="10" t="inlineStr">
         <is>
-          <t>日本漢字能力検定3級</t>
+          <t>計算技術検定1級</t>
         </is>
       </c>
       <c r="C14" s="12" t="n"/>
@@ -2823,12 +2823,12 @@
     <row r="15">
       <c r="A15" s="10" t="inlineStr">
         <is>
-          <t>漢検準2級</t>
+          <t>計算技術検定2級</t>
         </is>
       </c>
       <c r="B15" s="10" t="inlineStr">
         <is>
-          <t>日本漢字能力検定準2級</t>
+          <t>計算技術検定2級</t>
         </is>
       </c>
       <c r="C15" s="12" t="n"/>
@@ -2836,12 +2836,12 @@
     <row r="16">
       <c r="A16" s="10" t="inlineStr">
         <is>
-          <t>漢検2級</t>
+          <t>計算技術検定3級</t>
         </is>
       </c>
       <c r="B16" s="10" t="inlineStr">
         <is>
-          <t>日本漢字能力検定2級</t>
+          <t>計算技術検定3級</t>
         </is>
       </c>
       <c r="C16" s="12" t="n"/>
@@ -2849,12 +2849,12 @@
     <row r="17">
       <c r="A17" s="10" t="inlineStr">
         <is>
-          <t>数検3級</t>
+          <t>計算技術検定4級</t>
         </is>
       </c>
       <c r="B17" s="10" t="inlineStr">
         <is>
-          <t>実用数学技能検定3級</t>
+          <t>計算技術検定4級</t>
         </is>
       </c>
       <c r="C17" s="12" t="n"/>
@@ -2862,12 +2862,12 @@
     <row r="18">
       <c r="A18" s="10" t="inlineStr">
         <is>
-          <t>数検準2級</t>
+          <t>情報技術検定1級</t>
         </is>
       </c>
       <c r="B18" s="10" t="inlineStr">
         <is>
-          <t>実用数学技能検定準2級</t>
+          <t>情報技術検定1級</t>
         </is>
       </c>
       <c r="C18" s="12" t="n"/>
@@ -2875,12 +2875,12 @@
     <row r="19">
       <c r="A19" s="10" t="inlineStr">
         <is>
-          <t>乙4</t>
+          <t>情報技術検定2級</t>
         </is>
       </c>
       <c r="B19" s="10" t="inlineStr">
         <is>
-          <t>危険物取扱者乙種第4類</t>
+          <t>情報技術検定2級</t>
         </is>
       </c>
       <c r="C19" s="12" t="n"/>
@@ -2888,12 +2888,12 @@
     <row r="20">
       <c r="A20" s="10" t="inlineStr">
         <is>
-          <t>危険物乙4</t>
+          <t>情報技術検定3級</t>
         </is>
       </c>
       <c r="B20" s="10" t="inlineStr">
         <is>
-          <t>危険物取扱者乙種第4類</t>
+          <t>情報技術検定3級</t>
         </is>
       </c>
       <c r="C20" s="12" t="n"/>
@@ -2901,12 +2901,12 @@
     <row r="21">
       <c r="A21" s="10" t="inlineStr">
         <is>
-          <t>危険物取扱者乙種4類</t>
+          <t>初級CAD検定</t>
         </is>
       </c>
       <c r="B21" s="10" t="inlineStr">
         <is>
-          <t>危険物取扱者乙種第4類</t>
+          <t>初級CAD検定</t>
         </is>
       </c>
       <c r="C21" s="12" t="n"/>
@@ -2914,12 +2914,12 @@
     <row r="22">
       <c r="A22" s="10" t="inlineStr">
         <is>
-          <t>電工2種</t>
+          <t>基礎製図検定</t>
         </is>
       </c>
       <c r="B22" s="10" t="inlineStr">
         <is>
-          <t>第二種電気工事士</t>
+          <t>基礎製図検定</t>
         </is>
       </c>
       <c r="C22" s="12" t="n"/>
@@ -2927,12 +2927,12 @@
     <row r="23">
       <c r="A23" s="10" t="inlineStr">
         <is>
-          <t>第2種電気工事士</t>
+          <t>機械製図検定</t>
         </is>
       </c>
       <c r="B23" s="10" t="inlineStr">
         <is>
-          <t>第二種電気工事士</t>
+          <t>機械製図検定</t>
         </is>
       </c>
       <c r="C23" s="12" t="n"/>
@@ -2940,12 +2940,12 @@
     <row r="24">
       <c r="A24" s="10" t="inlineStr">
         <is>
-          <t>電気工事士2種</t>
+          <t>色彩検定３級</t>
         </is>
       </c>
       <c r="B24" s="10" t="inlineStr">
         <is>
-          <t>第二種電気工事士</t>
+          <t>色彩検定３級</t>
         </is>
       </c>
       <c r="C24" s="12" t="n"/>
@@ -2953,12 +2953,12 @@
     <row r="25">
       <c r="A25" s="10" t="inlineStr">
         <is>
-          <t>ガス溶接</t>
+          <t>色彩検定２級</t>
         </is>
       </c>
       <c r="B25" s="10" t="inlineStr">
         <is>
-          <t>ガス溶接技能講習修了</t>
+          <t>色彩検定２級</t>
         </is>
       </c>
       <c r="C25" s="12" t="n"/>
@@ -2966,12 +2966,12 @@
     <row r="26">
       <c r="A26" s="10" t="inlineStr">
         <is>
-          <t>アーク溶接</t>
+          <t>色彩検定UC級</t>
         </is>
       </c>
       <c r="B26" s="10" t="inlineStr">
         <is>
-          <t>アーク溶接等特別教育修了</t>
+          <t>色彩検定UC級</t>
         </is>
       </c>
       <c r="C26" s="12" t="n"/>
@@ -2979,12 +2979,12 @@
     <row r="27">
       <c r="A27" s="10" t="inlineStr">
         <is>
-          <t>アーク溶接特別教育修了</t>
+          <t>QC検定4級</t>
         </is>
       </c>
       <c r="B27" s="10" t="inlineStr">
         <is>
-          <t>アーク溶接等特別教育修了</t>
+          <t>QC検定4級</t>
         </is>
       </c>
       <c r="C27" s="12" t="n"/>
@@ -2992,12 +2992,12 @@
     <row r="28">
       <c r="A28" s="10" t="inlineStr">
         <is>
-          <t>フォークリフト</t>
+          <t>QC検定3級</t>
         </is>
       </c>
       <c r="B28" s="10" t="inlineStr">
         <is>
-          <t>フォークリフト運転技能講習修了</t>
+          <t>QC検定3級</t>
         </is>
       </c>
       <c r="C28" s="12" t="n"/>
@@ -3005,12 +3005,12 @@
     <row r="29">
       <c r="A29" s="10" t="inlineStr">
         <is>
-          <t>小型フォークリフト</t>
+          <t>日本語ワープロ検定2級</t>
         </is>
       </c>
       <c r="B29" s="10" t="inlineStr">
         <is>
-          <t>小型フォークリフト運転特別教育修了</t>
+          <t>日本語ワープロ検定2級</t>
         </is>
       </c>
       <c r="C29" s="12" t="n"/>
@@ -3018,12 +3018,12 @@
     <row r="30">
       <c r="A30" s="10" t="inlineStr">
         <is>
-          <t>玉掛け</t>
+          <t>日本語ワープロ検定準2級</t>
         </is>
       </c>
       <c r="B30" s="10" t="inlineStr">
         <is>
-          <t>玉掛け技能講習修了</t>
+          <t>日本語ワープロ検定準2級</t>
         </is>
       </c>
       <c r="C30" s="12" t="n"/>
@@ -3031,12 +3031,12 @@
     <row r="31">
       <c r="A31" s="10" t="inlineStr">
         <is>
-          <t>普通免許</t>
+          <t>日本語ワープロ検定3級</t>
         </is>
       </c>
       <c r="B31" s="10" t="inlineStr">
         <is>
-          <t>普通自動車第一種運転免許</t>
+          <t>日本語ワープロ検定3級</t>
         </is>
       </c>
       <c r="C31" s="12" t="n"/>
@@ -3044,12 +3044,12 @@
     <row r="32">
       <c r="A32" s="10" t="inlineStr">
         <is>
-          <t>普通自動車免許</t>
+          <t>日本語ワープロ検定4級</t>
         </is>
       </c>
       <c r="B32" s="10" t="inlineStr">
         <is>
-          <t>普通自動車第一種運転免許</t>
+          <t>日本語ワープロ検定4級</t>
         </is>
       </c>
       <c r="C32" s="12" t="n"/>
@@ -3057,12 +3057,12 @@
     <row r="33">
       <c r="A33" s="10" t="inlineStr">
         <is>
-          <t>原付</t>
+          <t>情報処理技能検定(表計算)4級</t>
         </is>
       </c>
       <c r="B33" s="10" t="inlineStr">
         <is>
-          <t>原動機付自転車運転免許</t>
+          <t>情報処理技能検定(表計算)4級</t>
         </is>
       </c>
       <c r="C33" s="12" t="n"/>
@@ -3070,12 +3070,12 @@
     <row r="34">
       <c r="A34" s="10" t="inlineStr">
         <is>
-          <t>基礎製図検定</t>
+          <t>文書デザイン検定4級</t>
         </is>
       </c>
       <c r="B34" s="10" t="inlineStr">
         <is>
-          <t>基礎製図検定</t>
+          <t>文書デザイン検定4級</t>
         </is>
       </c>
       <c r="C34" s="12" t="n"/>
@@ -3083,12 +3083,12 @@
     <row r="35">
       <c r="A35" s="10" t="inlineStr">
         <is>
-          <t>機械製図検定</t>
+          <t>プレゼンテーション作成検定3級</t>
         </is>
       </c>
       <c r="B35" s="10" t="inlineStr">
         <is>
-          <t>機械製図検定</t>
+          <t>プレゼンテーション作成検定3級</t>
         </is>
       </c>
       <c r="C35" s="12" t="n"/>
@@ -3096,12 +3096,12 @@
     <row r="36">
       <c r="A36" s="10" t="inlineStr">
         <is>
-          <t>計算技術検定3級</t>
+          <t>プレゼンテーション作成検定4級</t>
         </is>
       </c>
       <c r="B36" s="10" t="inlineStr">
         <is>
-          <t>計算技術検定3級</t>
+          <t>プレゼンテーション作成検定4級</t>
         </is>
       </c>
       <c r="C36" s="12" t="n"/>
@@ -3109,12 +3109,12 @@
     <row r="37">
       <c r="A37" s="10" t="inlineStr">
         <is>
-          <t>計算技術検定2級</t>
+          <t>パソコンスピード認定1級</t>
         </is>
       </c>
       <c r="B37" s="10" t="inlineStr">
         <is>
-          <t>計算技術検定2級</t>
+          <t>パソコンスピード認定1級</t>
         </is>
       </c>
       <c r="C37" s="12" t="n"/>
@@ -3122,12 +3122,12 @@
     <row r="38">
       <c r="A38" s="10" t="inlineStr">
         <is>
-          <t>情報技術検定3級</t>
+          <t>パソコンスピード認定2級</t>
         </is>
       </c>
       <c r="B38" s="10" t="inlineStr">
         <is>
-          <t>情報技術検定3級</t>
+          <t>パソコンスピード認定2級</t>
         </is>
       </c>
       <c r="C38" s="12" t="n"/>
@@ -3135,12 +3135,12 @@
     <row r="39">
       <c r="A39" s="10" t="inlineStr">
         <is>
-          <t>情報技術検定2級</t>
+          <t>パソコンスピード認定3級</t>
         </is>
       </c>
       <c r="B39" s="10" t="inlineStr">
         <is>
-          <t>情報技術検定2級</t>
+          <t>パソコンスピード認定3級</t>
         </is>
       </c>
       <c r="C39" s="12" t="n"/>
@@ -3148,12 +3148,12 @@
     <row r="40">
       <c r="A40" s="10" t="inlineStr">
         <is>
-          <t>技能検定3級</t>
+          <t>パソコンスピード認定4級</t>
         </is>
       </c>
       <c r="B40" s="10" t="inlineStr">
         <is>
-          <t>技能検定3級</t>
+          <t>パソコンスピード認定4級</t>
         </is>
       </c>
       <c r="C40" s="12" t="n"/>
@@ -3161,12 +3161,12 @@
     <row r="41">
       <c r="A41" s="10" t="inlineStr">
         <is>
-          <t>初級CAD検定</t>
+          <t>パソコンスピード認定5級</t>
         </is>
       </c>
       <c r="B41" s="10" t="inlineStr">
         <is>
-          <t>初級CAD検定</t>
+          <t>パソコンスピード認定5級</t>
         </is>
       </c>
       <c r="C41" s="12" t="n"/>
@@ -3174,12 +3174,12 @@
     <row r="42">
       <c r="A42" s="10" t="inlineStr">
         <is>
-          <t>QC検定3級</t>
+          <t>電気工事士第一種</t>
         </is>
       </c>
       <c r="B42" s="10" t="inlineStr">
         <is>
-          <t>品質管理検定3級</t>
+          <t>電気工事士第一種</t>
         </is>
       </c>
       <c r="C42" s="12" t="n"/>
@@ -3187,12 +3187,12 @@
     <row r="43">
       <c r="A43" s="10" t="inlineStr">
         <is>
-          <t>QC検定4級</t>
+          <t>電気工事士第二種</t>
         </is>
       </c>
       <c r="B43" s="10" t="inlineStr">
         <is>
-          <t>品質管理検定4級</t>
+          <t>電気工事士第二種</t>
         </is>
       </c>
       <c r="C43" s="12" t="n"/>
@@ -3200,12 +3200,12 @@
     <row r="44">
       <c r="A44" s="10" t="inlineStr">
         <is>
-          <t>日本語ワープロ検定3級</t>
+          <t>危険物取扱者乙1</t>
         </is>
       </c>
       <c r="B44" s="10" t="inlineStr">
         <is>
-          <t>日本語ワープロ検定3級</t>
+          <t>危険物取扱者乙1</t>
         </is>
       </c>
       <c r="C44" s="12" t="n"/>
@@ -3213,12 +3213,12 @@
     <row r="45">
       <c r="A45" s="10" t="inlineStr">
         <is>
-          <t>情報処理技能検定(表計算)4級</t>
+          <t>危険物取扱者乙2</t>
         </is>
       </c>
       <c r="B45" s="10" t="inlineStr">
         <is>
-          <t>情報処理技能検定試験 表計算4級</t>
+          <t>危険物取扱者乙2</t>
         </is>
       </c>
       <c r="C45" s="12" t="n"/>
@@ -3226,12 +3226,12 @@
     <row r="46">
       <c r="A46" s="10" t="inlineStr">
         <is>
-          <t>硬筆書写技能検定4級</t>
+          <t>危険物取扱者乙3</t>
         </is>
       </c>
       <c r="B46" s="10" t="inlineStr">
         <is>
-          <t>硬筆書写技能検定4級</t>
+          <t>危険物取扱者乙3</t>
         </is>
       </c>
       <c r="C46" s="12" t="n"/>
@@ -3239,15 +3239,353 @@
     <row r="47">
       <c r="A47" s="10" t="inlineStr">
         <is>
-          <t>簿記3級</t>
+          <t>危険物取扱者乙4</t>
         </is>
       </c>
       <c r="B47" s="10" t="inlineStr">
         <is>
-          <t>日商簿記検定3級</t>
+          <t>危険物取扱者乙4</t>
         </is>
       </c>
       <c r="C47" s="12" t="n"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="10" t="inlineStr">
+        <is>
+          <t>危険物取扱者乙5</t>
+        </is>
+      </c>
+      <c r="B48" s="10" t="inlineStr">
+        <is>
+          <t>危険物取扱者乙5</t>
+        </is>
+      </c>
+      <c r="C48" s="12" t="n"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="10" t="inlineStr">
+        <is>
+          <t>危険物取扱者乙6</t>
+        </is>
+      </c>
+      <c r="B49" s="10" t="inlineStr">
+        <is>
+          <t>危険物取扱者乙6</t>
+        </is>
+      </c>
+      <c r="C49" s="12" t="n"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="10" t="inlineStr">
+        <is>
+          <t>危険物取扱者丙</t>
+        </is>
+      </c>
+      <c r="B50" s="10" t="inlineStr">
+        <is>
+          <t>危険物取扱者丙</t>
+        </is>
+      </c>
+      <c r="C50" s="12" t="n"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="10" t="inlineStr">
+        <is>
+          <t>ガス溶接技能講習修了</t>
+        </is>
+      </c>
+      <c r="B51" s="10" t="inlineStr">
+        <is>
+          <t>ガス溶接技能講習修了</t>
+        </is>
+      </c>
+      <c r="C51" s="12" t="n"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="10" t="inlineStr">
+        <is>
+          <t>ボイラー取扱技能講習修了</t>
+        </is>
+      </c>
+      <c r="B52" s="10" t="inlineStr">
+        <is>
+          <t>ボイラー取扱技能講習修了</t>
+        </is>
+      </c>
+      <c r="C52" s="12" t="n"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="10" t="inlineStr">
+        <is>
+          <t>ア－ク溶接安全衛生教育修了</t>
+        </is>
+      </c>
+      <c r="B53" s="10" t="inlineStr">
+        <is>
+          <t>ア－ク溶接安全衛生教育修了</t>
+        </is>
+      </c>
+      <c r="C53" s="12" t="n"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="10" t="inlineStr">
+        <is>
+          <t>小型フォークリフト運転特別教育講習修了</t>
+        </is>
+      </c>
+      <c r="B54" s="10" t="inlineStr">
+        <is>
+          <t>小型フォークリフト運転特別教育講習修了</t>
+        </is>
+      </c>
+      <c r="C54" s="12" t="n"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="10" t="inlineStr">
+        <is>
+          <t>二級ボイラー技士2級</t>
+        </is>
+      </c>
+      <c r="B55" s="10" t="inlineStr">
+        <is>
+          <t>二級ボイラー技士2級</t>
+        </is>
+      </c>
+      <c r="C55" s="12" t="n"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="10" t="inlineStr">
+        <is>
+          <t>技能検定　機械加工（普通旋盤作業）2級</t>
+        </is>
+      </c>
+      <c r="B56" s="10" t="inlineStr">
+        <is>
+          <t>技能検定　機械加工（普通旋盤作業）2級</t>
+        </is>
+      </c>
+      <c r="C56" s="12" t="n"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="10" t="inlineStr">
+        <is>
+          <t>技能検定　機械加工（普通旋盤作業）3級</t>
+        </is>
+      </c>
+      <c r="B57" s="10" t="inlineStr">
+        <is>
+          <t>技能検定　機械加工（普通旋盤作業）3級</t>
+        </is>
+      </c>
+      <c r="C57" s="12" t="n"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="10" t="inlineStr">
+        <is>
+          <t>技能検定　機械検査（機械検査作業）2級</t>
+        </is>
+      </c>
+      <c r="B58" s="10" t="inlineStr">
+        <is>
+          <t>技能検定　機械検査（機械検査作業）2級</t>
+        </is>
+      </c>
+      <c r="C58" s="12" t="n"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="10" t="inlineStr">
+        <is>
+          <t>技能検定　機械検査（機械検査作業）3級</t>
+        </is>
+      </c>
+      <c r="B59" s="10" t="inlineStr">
+        <is>
+          <t>技能検定　機械検査（機械検査作業）3級</t>
+        </is>
+      </c>
+      <c r="C59" s="12" t="n"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="10" t="inlineStr">
+        <is>
+          <t>アーク溶接技能者適格性証明書Ａ－２Ｆ</t>
+        </is>
+      </c>
+      <c r="B60" s="10" t="inlineStr">
+        <is>
+          <t>アーク溶接技能者適格性証明書Ａ－２Ｆ</t>
+        </is>
+      </c>
+      <c r="C60" s="12" t="n"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="10" t="inlineStr">
+        <is>
+          <t>アーク溶接技能者適格性証明書Ａ－２V</t>
+        </is>
+      </c>
+      <c r="B61" s="10" t="inlineStr">
+        <is>
+          <t>アーク溶接技能者適格性証明書Ａ－２V</t>
+        </is>
+      </c>
+      <c r="C61" s="12" t="n"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="10" t="inlineStr">
+        <is>
+          <t>アーク溶接技能者適格性証明書Ｎ－２Ｆ</t>
+        </is>
+      </c>
+      <c r="B62" s="10" t="inlineStr">
+        <is>
+          <t>アーク溶接技能者適格性証明書Ｎ－２Ｆ</t>
+        </is>
+      </c>
+      <c r="C62" s="12" t="n"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="10" t="inlineStr">
+        <is>
+          <t>アーク溶接技能者適格性証明書Ａ－２H</t>
+        </is>
+      </c>
+      <c r="B63" s="10" t="inlineStr">
+        <is>
+          <t>アーク溶接技能者適格性証明書Ａ－２H</t>
+        </is>
+      </c>
+      <c r="C63" s="12" t="n"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="10" t="inlineStr">
+        <is>
+          <t>アーク溶接技能者適格性証明書SＮ－２Ｆ</t>
+        </is>
+      </c>
+      <c r="B64" s="10" t="inlineStr">
+        <is>
+          <t>アーク溶接技能者適格性証明書SＮ－２Ｆ</t>
+        </is>
+      </c>
+      <c r="C64" s="12" t="n"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="10" t="inlineStr">
+        <is>
+          <t>アーク溶接技能者適格性証明書T－1Ｆ</t>
+        </is>
+      </c>
+      <c r="B65" s="10" t="inlineStr">
+        <is>
+          <t>アーク溶接技能者適格性証明書T－1Ｆ</t>
+        </is>
+      </c>
+      <c r="C65" s="12" t="n"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="10" t="inlineStr">
+        <is>
+          <t>アーク溶接技能者適格性証明書SA－2Ｆ</t>
+        </is>
+      </c>
+      <c r="B66" s="10" t="inlineStr">
+        <is>
+          <t>アーク溶接技能者適格性証明書SA－2Ｆ</t>
+        </is>
+      </c>
+      <c r="C66" s="12" t="n"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="10" t="inlineStr">
+        <is>
+          <t>第二級デジタル通信</t>
+        </is>
+      </c>
+      <c r="B67" s="10" t="inlineStr">
+        <is>
+          <t>第二級デジタル通信</t>
+        </is>
+      </c>
+      <c r="C67" s="12" t="n"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="10" t="inlineStr">
+        <is>
+          <t>ジュニアマイスターゴールド</t>
+        </is>
+      </c>
+      <c r="B68" s="10" t="inlineStr">
+        <is>
+          <t>ジュニアマイスターゴールド</t>
+        </is>
+      </c>
+      <c r="C68" s="12" t="n"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="10" t="inlineStr">
+        <is>
+          <t>ジュニアマイスターシルバー</t>
+        </is>
+      </c>
+      <c r="B69" s="10" t="inlineStr">
+        <is>
+          <t>ジュニアマイスターシルバー</t>
+        </is>
+      </c>
+      <c r="C69" s="12" t="n"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="10" t="inlineStr">
+        <is>
+          <t>ジュニアマイスターブロンズ</t>
+        </is>
+      </c>
+      <c r="B70" s="10" t="inlineStr">
+        <is>
+          <t>ジュニアマイスターブロンズ</t>
+        </is>
+      </c>
+      <c r="C70" s="12" t="n"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="10" t="inlineStr">
+        <is>
+          <t>フォークリフト運転技能講習</t>
+        </is>
+      </c>
+      <c r="B71" s="10" t="inlineStr">
+        <is>
+          <t>フォークリフト運転技能講習</t>
+        </is>
+      </c>
+      <c r="C71" s="12" t="n"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="10" t="inlineStr">
+        <is>
+          <t>玉掛け技能講習</t>
+        </is>
+      </c>
+      <c r="B72" s="10" t="inlineStr">
+        <is>
+          <t>玉掛け技能講習</t>
+        </is>
+      </c>
+      <c r="C72" s="12" t="n"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="10" t="inlineStr">
+        <is>
+          <t>硬筆書写技能検定4級</t>
+        </is>
+      </c>
+      <c r="B73" s="10" t="inlineStr">
+        <is>
+          <t>硬筆書写技能検定4級</t>
+        </is>
+      </c>
+      <c r="C73" s="12" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/入力シート.xlsx
+++ b/入力シート.xlsx
@@ -4250,7 +4250,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A24"/>
+  <dimension ref="A1:A31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -4304,73 +4304,73 @@
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>3. python build_pdf.py            … 全員分のPDFを作る</t>
+          <t>3. このファイルを保存して閉じる（開いたままでも作れます）。</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">   python build_pdf.py --no 3     … No.3 の生徒だけ</t>
+          <t>4. 「履歴書PDF作成」を起動して、青い【PDF作成】ボタンを押す。</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">   python build_pdf.py --merge 3年2組_履歴書.pdf … 全員を1つのPDFにまとめる（印刷用）</t>
+          <t xml:space="preserve">   Windows … 履歴書PDF作成.bat をダブルクリック</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">   python watch.py                … 保存するたび自動で作り直す</t>
+          <t xml:space="preserve">   macOS  … 履歴書PDF作成.command をダブルクリック</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="14" t="inlineStr"/>
+      <c r="A12" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   ※ 画面では「全員／No.指定／氏名で絞り込み」「1つのPDFにまとめる」「自動更新」も選べます。</t>
+        </is>
+      </c>
     </row>
     <row r="13">
-      <c r="A13" s="13" t="inlineStr">
-        <is>
-          <t>■ 自動で入る項目</t>
-        </is>
-      </c>
+      <c r="A13" s="14" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="14" t="inlineStr">
-        <is>
-          <t>・満○歳 … 生年月日と基準日から自動計算します。</t>
+      <c r="A14" s="13" t="inlineStr">
+        <is>
+          <t>■ コマンドで使う場合（画面を使わないとき）</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="14" t="inlineStr">
         <is>
-          <t>・元号（昭和／平成／令和） … 生年月日から自動判定します。</t>
+          <t xml:space="preserve">   python build_pdf.py            … 全員分のPDFを作る</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="14" t="inlineStr">
         <is>
-          <t>・連絡先 … 空欄なら「同上」と印字します。</t>
+          <t xml:space="preserve">   python build_pdf.py --no 3     … No.3 の生徒だけ</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="14" t="inlineStr">
         <is>
-          <t>・郵便番号 … 7桁の数字だけでも 123-4567 の形に整えます。</t>
+          <t xml:space="preserve">   python build_pdf.py --merge 3年2組_履歴書.pdf … 全員を1つのPDFにまとめる（印刷用）</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="14" t="inlineStr">
         <is>
-          <t>・資格の取得年月 … 西暦で入力しても和暦（例: 令和6年6月）で印字します。</t>
+          <t xml:space="preserve">   python watch.py                … 保存するたび自動で作り直す</t>
         </is>
       </c>
     </row>
@@ -4380,33 +4380,78 @@
     <row r="20">
       <c r="A20" s="13" t="inlineStr">
         <is>
-          <t>■ 注意</t>
+          <t>■ 自動で入る項目</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="14" t="inlineStr">
         <is>
-          <t>・4行目は非表示のキー行です。読み取りに使うので、消したり並べ替えたりしないでください。</t>
+          <t>・満○歳 … 生年月日と基準日から自動計算します。</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="14" t="inlineStr">
         <is>
-          <t>・生徒を増やすときは、5行目以降の行をコピーして貼り付けてください。</t>
+          <t>・元号（昭和／平成／令和） … 生年月日から自動判定します。</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="14" t="inlineStr">
         <is>
-          <t>・列を増やすときは、4行目に同じ書き方のキー（license.7.name など）も入れてください。</t>
+          <t>・連絡先 … 空欄なら「同上」と印字します。</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="14" t="inlineStr">
+        <is>
+          <t>・郵便番号 … 7桁の数字だけでも 123-4567 の形に整えます。</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="14" t="inlineStr">
+        <is>
+          <t>・資格の取得年月 … 西暦で入力しても和暦（例: 令和6年6月）で印字します。</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="14" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="13" t="inlineStr">
+        <is>
+          <t>■ 注意</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="14" t="inlineStr">
+        <is>
+          <t>・4行目は非表示のキー行です。読み取りに使うので、消したり並べ替えたりしないでください。</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="14" t="inlineStr">
+        <is>
+          <t>・生徒を増やすときは、5行目以降の行をコピーして貼り付けてください。</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="14" t="inlineStr">
+        <is>
+          <t>・列を増やすときは、4行目に同じ書き方のキー（license.7.name など）も入れてください。</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="14" t="inlineStr">
         <is>
           <t>・写真は用紙の「写真をはる位置」に貼ってください（PDFには合成しません）。</t>
         </is>

--- a/入力シート.xlsx
+++ b/入力シート.xlsx
@@ -9,9 +9,10 @@
   <sheets>
     <sheet name="入力" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="設定" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="資格マスタ" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="資格取込" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="使い方" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="反映項目" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="資格マスタ" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="資格取込" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="使い方" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'入力'!$A$3:$AG$44</definedName>
@@ -107,7 +108,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -131,6 +132,9 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
@@ -2638,6 +2642,294 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:C17"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col hidden="1" width="13" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="9" t="inlineStr">
+        <is>
+          <t>反映項目（PDFに出す項目を選びます）</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>B列を「○」にした項目だけをPDFに書き込みます。「×」にすると、入力してあってもその欄は空欄のまま印刷されます（入力シートの値は消えません）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="11" t="inlineStr">
+        <is>
+          <t>項目</t>
+        </is>
+      </c>
+      <c r="B3" s="11" t="inlineStr">
+        <is>
+          <t>反映する（○／×）</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="12" t="inlineStr">
+        <is>
+          <t>氏名</t>
+        </is>
+      </c>
+      <c r="B4" s="13" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="12" t="inlineStr">
+        <is>
+          <t>ふりがな（氏名）</t>
+        </is>
+      </c>
+      <c r="B5" s="13" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>name_kana</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="12" t="inlineStr">
+        <is>
+          <t>生年月日・満○歳</t>
+        </is>
+      </c>
+      <c r="B6" s="13" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>birth</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="12" t="inlineStr">
+        <is>
+          <t>郵便番号</t>
+        </is>
+      </c>
+      <c r="B7" s="13" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>zip</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="12" t="inlineStr">
+        <is>
+          <t>住所</t>
+        </is>
+      </c>
+      <c r="B8" s="13" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>address</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="12" t="inlineStr">
+        <is>
+          <t>ふりがな（住所）</t>
+        </is>
+      </c>
+      <c r="B9" s="13" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>address_kana</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="12" t="inlineStr">
+        <is>
+          <t>連絡先（「同上」を含む）</t>
+        </is>
+      </c>
+      <c r="B10" s="13" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>contact</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="12" t="inlineStr">
+        <is>
+          <t>資格等</t>
+        </is>
+      </c>
+      <c r="B11" s="13" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>licenses</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="12" t="inlineStr">
+        <is>
+          <t>校内外の諸活動</t>
+        </is>
+      </c>
+      <c r="B12" s="13" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>activities</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="12" t="inlineStr">
+        <is>
+          <t>志望の動機</t>
+        </is>
+      </c>
+      <c r="B13" s="13" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>motivation</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="12" t="inlineStr">
+        <is>
+          <t>希望の職種</t>
+        </is>
+      </c>
+      <c r="B14" s="13" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>desired_job</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="12" t="inlineStr">
+        <is>
+          <t>アピールポイント</t>
+        </is>
+      </c>
+      <c r="B15" s="13" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>appeal</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="12" t="inlineStr">
+        <is>
+          <t>職歴</t>
+        </is>
+      </c>
+      <c r="B16" s="13" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="12" t="inlineStr">
+        <is>
+          <t>備考</t>
+        </is>
+      </c>
+      <c r="B17" s="13" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>remarks</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <dataValidations count="1">
+    <dataValidation sqref="B4 B5 B6 B7 B8 B9 B10 B11 B12 B13 B14 B15 B16 B17" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"○,×"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:C73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -3592,7 +3884,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4244,214 +4536,245 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A31"/>
+  <dimension ref="A1:A36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="13" t="inlineStr">
+      <c r="A1" s="14" t="inlineStr">
         <is>
           <t>■ このファイルについて</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="14" t="inlineStr">
+      <c r="A2" s="15" t="inlineStr">
         <is>
           <t>「入力」シートは 1行＝1生徒 の名列順です。クラス全員分をまとめて入力できます。</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="14" t="inlineStr">
+      <c r="A3" s="15" t="inlineStr">
         <is>
           <t>入力して保存したあと python build_pdf.py を実行すると、生徒ごとの履歴書PDFが 出力/ にできます。</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="14" t="inlineStr"/>
+      <c r="A4" s="15" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="13" t="inlineStr">
+      <c r="A5" s="14" t="inlineStr">
         <is>
           <t>■ 手順</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="14" t="inlineStr">
+      <c r="A6" s="15" t="inlineStr">
         <is>
           <t>1. 「入力」シートの黄色いセルに、名列順で入力する（氏名が空の行はPDFを作りません）。</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="14" t="inlineStr">
+      <c r="A7" s="15" t="inlineStr">
         <is>
           <t>2. 「設定」シートの基準日を確認する（満○歳の計算に使います）。</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="14" t="inlineStr">
+      <c r="A8" s="15" t="inlineStr">
         <is>
           <t>3. このファイルを保存して閉じる（開いたままでも作れます）。</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="14" t="inlineStr">
+      <c r="A9" s="15" t="inlineStr">
         <is>
           <t>4. 「履歴書PDF作成」を起動して、青い【PDF作成】ボタンを押す。</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="14" t="inlineStr">
+      <c r="A10" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">   Windows … 履歴書PDF作成.bat をダブルクリック</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="14" t="inlineStr">
+      <c r="A11" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">   macOS  … 履歴書PDF作成.command をダブルクリック</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="14" t="inlineStr">
+      <c r="A12" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">   ※ 画面では「全員／No.指定／氏名で絞り込み」「1つのPDFにまとめる」「自動更新」も選べます。</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="14" t="inlineStr"/>
+      <c r="A13" s="15" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="13" t="inlineStr">
+      <c r="A14" s="14" t="inlineStr">
         <is>
           <t>■ コマンドで使う場合（画面を使わないとき）</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="14" t="inlineStr">
+      <c r="A15" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">   python build_pdf.py            … 全員分のPDFを作る</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="14" t="inlineStr">
+      <c r="A16" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">   python build_pdf.py --no 3     … No.3 の生徒だけ</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="14" t="inlineStr">
+      <c r="A17" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">   python build_pdf.py --merge 3年2組_履歴書.pdf … 全員を1つのPDFにまとめる（印刷用）</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="14" t="inlineStr">
+      <c r="A18" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">   python watch.py                … 保存するたび自動で作り直す</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="14" t="inlineStr"/>
+      <c r="A19" s="15" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="13" t="inlineStr">
-        <is>
-          <t>■ 自動で入る項目</t>
+      <c r="A20" s="14" t="inlineStr">
+        <is>
+          <t>■ PDFに出す項目を選ぶ</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="14" t="inlineStr">
-        <is>
-          <t>・満○歳 … 生年月日と基準日から自動計算します。</t>
+      <c r="A21" s="15" t="inlineStr">
+        <is>
+          <t>「反映項目」シートで、項目ごとに ○（出す）／×（出さない）を選べます。</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="14" t="inlineStr">
-        <is>
-          <t>・元号（昭和／平成／令和） … 生年月日から自動判定します。</t>
+      <c r="A22" s="15" t="inlineStr">
+        <is>
+          <t>×にした欄は、入力してあってもPDFでは空欄のままになります（入力シートの値は消えません）。</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="14" t="inlineStr">
-        <is>
-          <t>・連絡先 … 空欄なら「同上」と印字します。</t>
+      <c r="A23" s="15" t="inlineStr">
+        <is>
+          <t>画面（履歴書PDF作成）のチェックボックスでも、その場で切り替えられます。</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="14" t="inlineStr">
-        <is>
-          <t>・郵便番号 … 7桁の数字だけでも 123-4567 の形に整えます。</t>
-        </is>
-      </c>
+      <c r="A24" s="15" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="14" t="inlineStr">
         <is>
+          <t>■ 自動で入る項目</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="15" t="inlineStr">
+        <is>
+          <t>・満○歳 … 生年月日と基準日から自動計算します。</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="15" t="inlineStr">
+        <is>
+          <t>・元号（昭和／平成／令和） … 生年月日から自動判定します。</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="15" t="inlineStr">
+        <is>
+          <t>・連絡先 … 空欄なら「同上」と印字します。</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="15" t="inlineStr">
+        <is>
+          <t>・郵便番号 … 7桁の数字だけでも 123-4567 の形に整えます。</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="15" t="inlineStr">
+        <is>
           <t>・資格の取得年月 … 西暦で入力しても和暦（例: 令和6年6月）で印字します。</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="14" t="inlineStr"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="13" t="inlineStr">
+    <row r="31">
+      <c r="A31" s="15" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="14" t="inlineStr">
         <is>
           <t>■ 注意</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="14" t="inlineStr">
+    <row r="33">
+      <c r="A33" s="15" t="inlineStr">
         <is>
           <t>・4行目は非表示のキー行です。読み取りに使うので、消したり並べ替えたりしないでください。</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="14" t="inlineStr">
+    <row r="34">
+      <c r="A34" s="15" t="inlineStr">
         <is>
           <t>・生徒を増やすときは、5行目以降の行をコピーして貼り付けてください。</t>
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="14" t="inlineStr">
+    <row r="35">
+      <c r="A35" s="15" t="inlineStr">
         <is>
           <t>・列を増やすときは、4行目に同じ書き方のキー（license.7.name など）も入れてください。</t>
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="14" t="inlineStr">
+    <row r="36">
+      <c r="A36" s="15" t="inlineStr">
         <is>
           <t>・写真は用紙の「写真をはる位置」に貼ってください（PDFには合成しません）。</t>
         </is>
